--- a/hardware/材料清单.xlsx
+++ b/hardware/材料清单.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DevelopmentProject\ROBOOT\spotMicro-Chinese\硬件部分\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DevelopmentProject\ROBOOT\SpotMicro\spotMicro-Chinese\hardware\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24464CED-07F4-4788-9058-7A9AB8B80773}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E48BDFC-5364-4D2D-ADAF-D2A201DCE0ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
   <si>
     <t>Spot Micro 四足机器狗材料清单</t>
   </si>
@@ -207,6 +207,14 @@
   </si>
   <si>
     <t>https://item.taobao.com/item.htm?abbucket=8&amp;id=717517344390&amp;mi_id=0000YQyhwcOFZHfU2DV0zGm162xNMDW568mIoqZGtaLDe64&amp;ns=1&amp;priceTId=2100c90417732230668148450e0cdc&amp;skuId=5178734242961&amp;spm=a21n57.1.hoverItem.12&amp;utparam=%7B%22aplus_abtest%22%3A%2279e023bebacc64df8e77f91bff263273%22%7D&amp;xxc=taobaoSearch</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>资料</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://docs.m5stack.com/zh_CN/module/servo2</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -611,17 +619,18 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="41.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6.5546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="5.5546875" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="27.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="83.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="55.44140625" customWidth="1"/>
+    <col min="6" max="6" width="11.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -630,7 +639,7 @@
       <c r="D1" s="8"/>
       <c r="E1" s="8"/>
     </row>
-    <row r="2" spans="1:5" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -646,8 +655,11 @@
       <c r="E2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -664,7 +676,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -677,8 +689,11 @@
       <c r="E4" s="3" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F4" s="7" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>40</v>
       </c>
@@ -695,7 +710,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>47</v>
       </c>
@@ -712,7 +727,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>39</v>
       </c>
@@ -726,7 +741,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -743,7 +758,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>49</v>
       </c>
@@ -760,7 +775,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>10</v>
       </c>
@@ -777,7 +792,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>11</v>
       </c>
@@ -794,7 +809,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>22</v>
       </c>
@@ -811,7 +826,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>26</v>
       </c>
@@ -828,11 +843,11 @@
         <v>38</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C14" s="2"/>
       <c r="E14" s="3"/>
     </row>
-    <row r="15" spans="1:5" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -846,7 +861,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>14</v>
       </c>
@@ -944,6 +959,7 @@
     <hyperlink ref="E13" r:id="rId9" display="https://item.taobao.com/item.htm?abbucket=8&amp;id=40138107032&amp;mi_id=0000wjDKWqbOPL4ccP5OkWcVT_OFck6RMQWZ3L6QxS3pw1g&amp;ns=1&amp;priceTId=2100c87a17730469940756678e0ce8&amp;skuId=4096008947713&amp;spm=a21n57.1.hoverItem.2&amp;utparam=%7B%22aplus_abtest%22%3A%22904b5bfb6c4050e69646dfefb0bbf9e4%22%7D&amp;xxc=taobaoSearch" xr:uid="{10C41FCA-980A-4157-89C1-900422E8A8BB}"/>
     <hyperlink ref="E6" r:id="rId10" display="https://detail.tmall.com/item.htm?abbucket=8&amp;id=661479387602&amp;mi_id=0000ugn8-RABHKtkJfnJXPIEqPFjOEAuUZIFRu_r0Csr9mY&amp;ns=1&amp;priceTId=2100c91217732135001816670e0d28&amp;skuId=6114653719083&amp;spm=a21n57.1.hoverItem.2&amp;utparam=%7B%22aplus_abtest%22%3A%22a4b18caf5224b8f918e6e93295e7d3cf%22%7D&amp;xxc=taobaoSearch" xr:uid="{8F2C6138-8387-4BCC-8C1C-247842195234}"/>
     <hyperlink ref="E9" r:id="rId11" display="https://item.taobao.com/item.htm?abbucket=8&amp;id=717517344390&amp;mi_id=0000YQyhwcOFZHfU2DV0zGm162xNMDW568mIoqZGtaLDe64&amp;ns=1&amp;priceTId=2100c90417732230668148450e0cdc&amp;skuId=5178734242961&amp;spm=a21n57.1.hoverItem.12&amp;utparam=%7B%22aplus_abtest%22%3A%2279e023bebacc64df8e77f91bff263273%22%7D&amp;xxc=taobaoSearch" xr:uid="{543FF516-10F6-4F91-800B-E2AED8967BBE}"/>
+    <hyperlink ref="F4" r:id="rId12" xr:uid="{F033C7A7-B516-442F-A69E-4814E6229A17}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/hardware/材料清单.xlsx
+++ b/hardware/材料清单.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DevelopmentProject\ROBOOT\SpotMicro\spotMicro-Chinese\hardware\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E48BDFC-5364-4D2D-ADAF-D2A201DCE0ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7B3C60C-CF63-4F26-9A77-D273D9E8408E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="55">
   <si>
     <t>Spot Micro 四足机器狗材料清单</t>
   </si>
@@ -215,6 +215,10 @@
   </si>
   <si>
     <t>https://docs.m5stack.com/zh_CN/module/servo2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.yahboom.com/study/RPLIDAR_SLAMTEC 提取码：32fm</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -726,6 +730,9 @@
       <c r="E6" s="7" t="s">
         <v>45</v>
       </c>
+      <c r="F6" s="7" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="7" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
@@ -960,6 +967,7 @@
     <hyperlink ref="E6" r:id="rId10" display="https://detail.tmall.com/item.htm?abbucket=8&amp;id=661479387602&amp;mi_id=0000ugn8-RABHKtkJfnJXPIEqPFjOEAuUZIFRu_r0Csr9mY&amp;ns=1&amp;priceTId=2100c91217732135001816670e0d28&amp;skuId=6114653719083&amp;spm=a21n57.1.hoverItem.2&amp;utparam=%7B%22aplus_abtest%22%3A%22a4b18caf5224b8f918e6e93295e7d3cf%22%7D&amp;xxc=taobaoSearch" xr:uid="{8F2C6138-8387-4BCC-8C1C-247842195234}"/>
     <hyperlink ref="E9" r:id="rId11" display="https://item.taobao.com/item.htm?abbucket=8&amp;id=717517344390&amp;mi_id=0000YQyhwcOFZHfU2DV0zGm162xNMDW568mIoqZGtaLDe64&amp;ns=1&amp;priceTId=2100c90417732230668148450e0cdc&amp;skuId=5178734242961&amp;spm=a21n57.1.hoverItem.12&amp;utparam=%7B%22aplus_abtest%22%3A%2279e023bebacc64df8e77f91bff263273%22%7D&amp;xxc=taobaoSearch" xr:uid="{543FF516-10F6-4F91-800B-E2AED8967BBE}"/>
     <hyperlink ref="F4" r:id="rId12" xr:uid="{F033C7A7-B516-442F-A69E-4814E6229A17}"/>
+    <hyperlink ref="F6" r:id="rId13" xr:uid="{D79DE92C-9686-465A-AB18-DA4FB6CCD9A6}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
